--- a/PTPseminarLNv2/PTPseminarLNv2.xlsx
+++ b/PTPseminarLNv2/PTPseminarLNv2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Asus-PC\OneDrive\Documents\GitHub\opet\PTPseminarLNv2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{0A2499D5-186C-4D0D-92D2-D272732B916B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4F0E7F0-85E5-4ED0-A21D-8765E46E9B25}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{2C7297CB-2BB8-41FD-8AD1-E0FC650C707D}"/>
   </bookViews>
